--- a/NFIFProsjekt/tilbud/PRISANSLAG.xlsx
+++ b/NFIFProsjekt/tilbud/PRISANSLAG.xlsx
@@ -25,15 +25,15 @@
     <author>Claude</author>
   </authors>
   <commentList>
-    <comment ref="A5" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Prismodellen aug. 2026: kostnad 840 000–1 020 000 (1 080–1 490 timer).</t>
+    <comment ref="A6" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Verdien av det som er bygget: plattform, 1,4 mill. resultater, daglig import. Ditt valg.</t>
         </r>
       </text>
     </comment>
@@ -45,43 +45,139 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
+          <t xml:space="preserve">Gap-analysen: 80–120 timer inkl. rekordgodkjenning.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A9" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Gap-analysen: 180–320 timer. Omfanget må avgrenses i avtalen.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A10" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Gap-analysen: 80–120 timer.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Gap-analysen: 120–160 timer.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Gap-analysen: 120–160 timer.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Gap-analysen: 60–90 timer.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A18" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
           <t xml:space="preserve">Infrastruktur i prismodellen: 63 000–135 000 per år.</t>
         </r>
       </text>
     </comment>
-    <comment ref="A9" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Ca. 250 timer forvaltning i prismodellen: 150 000–200 000.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A15" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Den delen som kan sammenlignes med en ren statistikklisens.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A36" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Danmark: «Statistik» 128 000–177 000 DKK/år 2020–22 (ca. 200 000–275 000 NOK). Se 10_KONKURRENT_PRISER.md.</t>
+    <comment ref="A19" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Prismodellen: ca. 250 timer forvaltning, 150 000–200 000.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A21" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Infrastruktur 63–135k + forvaltning 150–200k. Skal ikke sendes.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A24" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Gap-analysen: 360–520 timer.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A44" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Danmark: «Statistik» ca. 200 000–275 000 NOK/år 2020–22. Se 10_KONKURRENT_PRISER.md.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A47" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Venstre: mot høy kostnad. Høyre: mot lav kostnad.</t>
         </r>
       </text>
     </comment>
@@ -90,7 +186,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="42">
   <si>
     <t xml:space="preserve">Prisanslag til NFIF · statistikkplattform</t>
   </si>
@@ -98,40 +194,58 @@
     <t xml:space="preserve">Gule celler med blå tekst kan endres. Resten regnes ut. Alle beløp eks. mva.</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Etablering frem til operativ løsning 01.01.2027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Etablering, fastpris</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Årlig drift og forvaltning, fastpris</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drift i EU/EØS, overvåking, sikkerhetskopi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daglig import, kvalitetskontroll og support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Videreutvikling som NFIF prioriterer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Antall timer i potten</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Tilsvarer timepris</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analyse: to mesterskapspakker og én årsrapport</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sum årlig drift</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Herav plattform, uten utvikling og analyse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Utvikling utenfor fastprisen</t>
+    <t xml:space="preserve">1. Nasjonal banestatistikk · etablering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Det som finnes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plattform og datagrunnlag, overført til NFIF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Det som mangler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Masters: femårsklasser, WMA-regler og rekorder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eldre statistikk: opphenting og kontroll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dokumentasjon, DPIA og databehandleravtale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minstekrav i kravspekken §22 som ikke er bygget</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kvalitetsnivå A/B/C for resultater</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dokumentert API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kretsstatistikk (krever klubb-til-krets fra NFIF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sum etablering banestatistikk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Nasjonal banestatistikk · årlig</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drift i EU/EØS, overvåking og sikkerhetskopi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registrering av resultater og vedlikehold av basen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sum årlig banestatistikk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Kostnad i prismodellen, lav og høy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Gateløp · separat pris</t>
   </si>
   <si>
     <t xml:space="preserve">Lav</t>
@@ -140,49 +254,52 @@
     <t xml:space="preserve">Høy</t>
   </si>
   <si>
+    <t xml:space="preserve">Etablering, etter kartlegging av tidtakernes data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Årlig registrering og vedlikehold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Tillegg, bestilles ved behov</t>
+  </si>
+  <si>
     <t xml:space="preserve">Integrasjon mot eksternt system, per system</t>
   </si>
   <si>
-    <t xml:space="preserve">Løp utenfor bane, full leveranse</t>
-  </si>
-  <si>
     <t xml:space="preserve">Aktivitetsmodul og dashbord for forbund og kretser</t>
   </si>
   <si>
-    <t xml:space="preserve">Historisk utvidelse 2001–2012, inkl. kartlegging</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Timepris, øvrig utvikling</t>
+    <t xml:space="preserve">Analyse per år: to mesterskapspakker og én årsrapport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Timepris, utvikling</t>
   </si>
   <si>
     <t xml:space="preserve">Timepris, analyse og utredning</t>
   </si>
   <si>
-    <t xml:space="preserve">4. Samlet over fem år</t>
+    <t xml:space="preserve">5. Samlet over fem år</t>
   </si>
   <si>
     <t xml:space="preserve">Antall driftsår</t>
   </si>
   <si>
-    <t xml:space="preserve">Integrasjoner i realistisk scenario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integrasjoner i fullt scenario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A. Etablering og drift</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B. + løp utenfor bane, integrasjoner og aktivitetsmodul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C. Alle postene i punkt 3</t>
+    <t xml:space="preserve">Integrasjoner i scenario C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A. Banestatistikk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B. Banestatistikk og gateløp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C. B + analyse, aktivitetsmodul og integrasjoner</t>
   </si>
   <si>
     <t xml:space="preserve">Før KPI-regulering fra år fire.</t>
   </si>
   <si>
-    <t xml:space="preserve">5. Til sammenligning (skal ikke sendes)</t>
+    <t xml:space="preserve">6. Til sammenligning (skal ikke sendes)</t>
   </si>
   <si>
     <t xml:space="preserve">Tilastopaja-nivå per år, anslag</t>
@@ -191,23 +308,22 @@
     <t xml:space="preserve">Tilastopaja-nivå over fem år</t>
   </si>
   <si>
-    <t xml:space="preserve">Vår plattformdel per år (punkt 2, herav plattform)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vår fastpris over fem år (scenario A)</t>
+    <t xml:space="preserve">Vår årspris banestatistikk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Margin per år på banestatistikk mot kostnad</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot; kr&quot;;\-#,##0&quot; kr&quot;;\-"/>
-    <numFmt numFmtId="166" formatCode="#,##0&quot; t&quot;"/>
-    <numFmt numFmtId="167" formatCode="0"/>
+    <numFmt numFmtId="166" formatCode="0"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -233,13 +349,6 @@
     <font>
       <b val="true"/>
       <sz val="14"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -340,7 +449,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -361,39 +470,31 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -649,7 +750,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58"/>
@@ -660,360 +761,363 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="6" t="n">
-        <v>950000</v>
-      </c>
-      <c r="C5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
+      <c r="A6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>250000</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
+      <c r="A7" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="6" t="n">
+      <c r="A8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>140000</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>140000</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="7" t="n">
+        <f aca="false">B6+SUM(B8:B10)+SUM(B12:B14)</f>
+        <v>980000</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="5" t="n">
         <v>90000</v>
       </c>
-      <c r="C8" s="2"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>170000</v>
-      </c>
-      <c r="C9" s="2"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="6" t="n">
-        <v>140000</v>
-      </c>
-      <c r="C10" s="2"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="7" t="n">
-        <v>175</v>
-      </c>
-      <c r="C11" s="2"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="8" t="n">
-        <f aca="false">IF(B11=0,0,B10/B11)</f>
-        <v>800</v>
-      </c>
-      <c r="C12" s="2"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" s="6" t="n">
-        <v>80000</v>
-      </c>
-      <c r="C13" s="2"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" s="10" t="n">
-        <f aca="false">SUM(B8:B10)+B13</f>
-        <v>480000</v>
-      </c>
-      <c r="C14" s="2"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="8" t="n">
-        <f aca="false">B8+B9</f>
-        <v>260000</v>
-      </c>
-      <c r="C15" s="2"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="6" t="n">
-        <v>90000</v>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>150000</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="s">
+      <c r="B19" s="5" t="n">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B20" s="7" t="n">
+        <f aca="false">B18+B19</f>
+        <v>290000</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>213000</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>335000</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="5" t="n">
         <v>450000</v>
       </c>
-      <c r="C19" s="6" t="n">
+      <c r="C24" s="5" t="n">
         <v>600000</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" s="6" t="n">
-        <v>200000</v>
-      </c>
-      <c r="C20" s="6" t="n">
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" s="6" t="n">
-        <v>200000</v>
-      </c>
-      <c r="C21" s="6" t="n">
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="6" t="n">
-        <v>950</v>
-      </c>
-      <c r="C22" s="2"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" s="6" t="n">
-        <v>1100</v>
-      </c>
-      <c r="C23" s="2"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B26" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="C26" s="2"/>
+      <c r="B25" s="5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>100000</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B27" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C27" s="2"/>
+      <c r="B27" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B28" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="C28" s="2"/>
+      <c r="B28" s="5" t="n">
+        <v>90000</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>150000</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2"/>
-      <c r="B29" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>15</v>
+      <c r="A29" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>200000</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>300000</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B30" s="13" t="n">
-        <f aca="false">B5+B26*B14</f>
-        <v>3350000</v>
-      </c>
-      <c r="C30" s="13" t="n">
-        <f aca="false">B5+B26*B14</f>
-        <v>3350000</v>
+      <c r="A30" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>80000</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>80000</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B31" s="13" t="n">
-        <f aca="false">B30+B19+B27*B18+B20</f>
-        <v>4180000</v>
-      </c>
-      <c r="C31" s="13" t="n">
-        <f aca="false">C30+C19+B27*C18+C20</f>
-        <v>4550000</v>
+      <c r="A31" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>950</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B32" s="13" t="n">
-        <f aca="false">B30+B19+B28*B18+B20+B21</f>
-        <v>4650000</v>
-      </c>
-      <c r="C32" s="13" t="n">
-        <f aca="false">C30+C19+B28*C18+C20+C21</f>
-        <v>5300000</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3" t="s">
+      <c r="A32" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
+      <c r="B32" s="5" t="n">
+        <v>1100</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
+      <c r="A34" s="3" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B35" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>15</v>
+        <v>31</v>
+      </c>
+      <c r="B35" s="9" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B36" s="6" t="n">
+      <c r="A36" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B36" s="9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B38" s="10" t="n">
+        <f aca="false">B15+B35*B20</f>
+        <v>2430000</v>
+      </c>
+      <c r="C38" s="10" t="n">
+        <f aca="false">B15+B35*B20</f>
+        <v>2430000</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B39" s="10" t="n">
+        <f aca="false">B38+B24+B35*B25</f>
+        <v>3380000</v>
+      </c>
+      <c r="C39" s="10" t="n">
+        <f aca="false">C38+C24+B35*C25</f>
+        <v>3530000</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B40" s="10" t="n">
+        <f aca="false">B39+B35*B30+B29+B36*B28</f>
+        <v>4160000</v>
+      </c>
+      <c r="C40" s="10" t="n">
+        <f aca="false">C39+B35*C30+C29+B36*C28</f>
+        <v>4530000</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="5" t="n">
         <v>150000</v>
       </c>
-      <c r="C36" s="6" t="n">
+      <c r="C44" s="5" t="n">
         <v>300000</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B37" s="8" t="n">
-        <f aca="false">B36*B26</f>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="11" t="n">
+        <f aca="false">B44*B35</f>
         <v>750000</v>
       </c>
-      <c r="C37" s="8" t="n">
-        <f aca="false">C36*B26</f>
+      <c r="C45" s="11" t="n">
+        <f aca="false">C44*B35</f>
         <v>1500000</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B38" s="8" t="n">
-        <f aca="false">B15</f>
-        <v>260000</v>
-      </c>
-      <c r="C38" s="8" t="n">
-        <f aca="false">B15</f>
-        <v>260000</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B39" s="8" t="n">
-        <f aca="false">B30</f>
-        <v>3350000</v>
-      </c>
-      <c r="C39" s="8" t="n">
-        <f aca="false">C30</f>
-        <v>3350000</v>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="11" t="n">
+        <f aca="false">B20</f>
+        <v>290000</v>
+      </c>
+      <c r="C46" s="11" t="n">
+        <f aca="false">B20</f>
+        <v>290000</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="11" t="n">
+        <f aca="false">B20-C21</f>
+        <v>-45000</v>
+      </c>
+      <c r="C47" s="11" t="n">
+        <f aca="false">B20-B21</f>
+        <v>77000</v>
       </c>
     </row>
   </sheetData>
